--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0005_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0005_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -1113,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0</v>
       </c>
       <c r="G28" s="0">
         <v>0</v>
@@ -1122,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0</v>
       </c>
       <c r="J28" s="0">
         <v>0</v>
@@ -1151,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="0">
-        <v>0.0018193064803696914</v>
+        <v>0</v>
       </c>
       <c r="G29" s="0">
         <v>0</v>
@@ -1174,31 +1175,31 @@
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0</v>
       </c>
       <c r="B30" s="0">
         <v>0</v>
       </c>
       <c r="C30" s="0">
-        <v>0.0050723443107318078</v>
+        <v>0</v>
       </c>
       <c r="D30" s="0">
         <v>0</v>
       </c>
       <c r="E30" s="0">
-        <v>0.001790029535487334</v>
+        <v>0</v>
       </c>
       <c r="F30" s="0">
-        <v>0.0036386129607393625</v>
+        <v>0</v>
       </c>
       <c r="G30" s="0">
         <v>0</v>
       </c>
       <c r="H30" s="0">
-        <v>0.005680849855138323</v>
+        <v>0</v>
       </c>
       <c r="I30" s="0">
-        <v>0.0039721157474528774</v>
+        <v>0</v>
       </c>
       <c r="J30" s="0">
         <v>0</v>
@@ -1207,2667 +1208,2667 @@
         <v>0</v>
       </c>
       <c r="L30" s="0">
-        <v>0.0015550648462040854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>0.0049227133996258693</v>
+        <v>0</v>
       </c>
       <c r="B31" s="0">
         <v>0</v>
       </c>
       <c r="C31" s="0">
-        <v>0.015217032932195423</v>
+        <v>0</v>
       </c>
       <c r="D31" s="0">
-        <v>0.014425504291587513</v>
+        <v>0</v>
       </c>
       <c r="E31" s="0">
-        <v>0.003580059070974668</v>
+        <v>0.0029833825591455568</v>
       </c>
       <c r="F31" s="0">
-        <v>0.030928210166284584</v>
+        <v>0</v>
       </c>
       <c r="G31" s="0">
         <v>0</v>
       </c>
       <c r="H31" s="0">
-        <v>0.017042549565414972</v>
+        <v>0</v>
       </c>
       <c r="I31" s="0">
-        <v>0.021846636610990827</v>
+        <v>0</v>
       </c>
       <c r="J31" s="0">
-        <v>0.018402649981597335</v>
+        <v>0</v>
       </c>
       <c r="K31" s="0">
         <v>0</v>
       </c>
       <c r="L31" s="0">
-        <v>0.0046651945386122556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>0.027074923697942281</v>
+        <v>0</v>
       </c>
       <c r="B32" s="0">
         <v>0</v>
       </c>
       <c r="C32" s="0">
-        <v>0.034238324097439703</v>
+        <v>0</v>
       </c>
       <c r="D32" s="0">
-        <v>0.019234005722116688</v>
+        <v>0</v>
       </c>
       <c r="E32" s="0">
-        <v>0.016706942331215117</v>
+        <v>0.0041767355828037792</v>
       </c>
       <c r="F32" s="0">
-        <v>0.10188116290070216</v>
+        <v>0.0018193064803696812</v>
       </c>
       <c r="G32" s="0">
-        <v>0.040233353450010022</v>
+        <v>0</v>
       </c>
       <c r="H32" s="0">
-        <v>0.05680849855138323</v>
+        <v>0</v>
       </c>
       <c r="I32" s="0">
-        <v>0.03972115747452877</v>
+        <v>0</v>
       </c>
       <c r="J32" s="0">
-        <v>0.018402649981597335</v>
+        <v>0</v>
       </c>
       <c r="K32" s="0">
         <v>0</v>
       </c>
       <c r="L32" s="0">
-        <v>0.021770907846857195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>0.08614748449345272</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B33" s="0">
         <v>0</v>
       </c>
       <c r="C33" s="0">
-        <v>0.11539583306914862</v>
+        <v>0.0025361721553659039</v>
       </c>
       <c r="D33" s="0">
-        <v>0.062510518596879228</v>
+        <v>0.002404250715264586</v>
       </c>
       <c r="E33" s="0">
-        <v>0.037590620245234012</v>
+        <v>0.017900295354873339</v>
       </c>
       <c r="F33" s="0">
-        <v>0.18193064803696812</v>
+        <v>0.0090965324018484079</v>
       </c>
       <c r="G33" s="0">
-        <v>0.060350030175015036</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H33" s="0">
-        <v>0.16474464579901138</v>
+        <v>0</v>
       </c>
       <c r="I33" s="0">
-        <v>0.1648428035192944</v>
+        <v>0.0099302893686321926</v>
       </c>
       <c r="J33" s="0">
-        <v>0.03680529996319467</v>
+        <v>0</v>
       </c>
       <c r="K33" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L33" s="0">
-        <v>0.051317139924734814</v>
+        <v>0.0031101296924081708</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>0.19690853598503477</v>
+        <v>0</v>
       </c>
       <c r="B34" s="0">
         <v>0.17543859649122792</v>
       </c>
       <c r="C34" s="0">
-        <v>0.22064697751683363</v>
+        <v>0.0038042582330488559</v>
       </c>
       <c r="D34" s="0">
-        <v>0.15146779506166888</v>
+        <v>0.0072127521457937566</v>
       </c>
       <c r="E34" s="0">
-        <v>0.080551329096930024</v>
+        <v>0.054297562576449132</v>
       </c>
       <c r="F34" s="0">
-        <v>0.4220791034457661</v>
+        <v>0.0090965324018484079</v>
       </c>
       <c r="G34" s="0">
-        <v>0.16093341380004009</v>
+        <v>0.080466706900020044</v>
       </c>
       <c r="H34" s="0">
-        <v>0.4317445889905126</v>
+        <v>0.005680849855138323</v>
       </c>
       <c r="I34" s="0">
-        <v>0.29790868105896579</v>
+        <v>0.029790868105896578</v>
       </c>
       <c r="J34" s="0">
-        <v>0.165623849834376</v>
+        <v>0</v>
       </c>
       <c r="K34" s="0">
-        <v>0.38659793814432958</v>
+        <v>0</v>
       </c>
       <c r="L34" s="0">
-        <v>0.12596025254253093</v>
+        <v>0.024881037539265367</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>0.43812149256670485</v>
+        <v>0.014768140198877689</v>
       </c>
       <c r="B35" s="0">
         <v>0</v>
       </c>
       <c r="C35" s="0">
-        <v>0.43748969680062083</v>
+        <v>0.010144688621463673</v>
       </c>
       <c r="D35" s="0">
-        <v>0.37746736229654204</v>
+        <v>0.024042507152645991</v>
       </c>
       <c r="E35" s="0">
-        <v>0.20466004355738629</v>
+        <v>0.12589874399594317</v>
       </c>
       <c r="F35" s="0">
-        <v>0.73863843103009486</v>
+        <v>0.038205436087763521</v>
       </c>
       <c r="G35" s="0">
-        <v>0.24140012070006148</v>
+        <v>0.1005833836250256</v>
       </c>
       <c r="H35" s="0">
-        <v>0.74987218087826291</v>
+        <v>0.0056808498551383551</v>
       </c>
       <c r="I35" s="0">
-        <v>0.59978947786538783</v>
+        <v>0.07348414132787863</v>
       </c>
       <c r="J35" s="0">
-        <v>0.23923444976076666</v>
+        <v>0</v>
       </c>
       <c r="K35" s="0">
-        <v>1.0309278350515512</v>
+        <v>0</v>
       </c>
       <c r="L35" s="0">
-        <v>0.32500855285665564</v>
+        <v>0.080863372002612885</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>0.86885891503396606</v>
+        <v>0.027074923697942281</v>
       </c>
       <c r="B36" s="0">
-        <v>0.52631578947368374</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C36" s="0">
-        <v>0.85849427459135852</v>
+        <v>0.038042582330488559</v>
       </c>
       <c r="D36" s="0">
-        <v>0.79580698675257788</v>
+        <v>0.098574279325848016</v>
       </c>
       <c r="E36" s="0">
-        <v>0.44691070736000438</v>
+        <v>0.28103463707151144</v>
       </c>
       <c r="F36" s="0">
-        <v>1.3590219408361521</v>
+        <v>0.096423243459593119</v>
       </c>
       <c r="G36" s="0">
-        <v>0.54315027157513529</v>
+        <v>0.16093341380004009</v>
       </c>
       <c r="H36" s="0">
-        <v>1.5167869113219323</v>
+        <v>0.039765948985968268</v>
       </c>
       <c r="I36" s="0">
-        <v>1.0963039462969941</v>
+        <v>0.22045242398363471</v>
       </c>
       <c r="J36" s="0">
-        <v>0.66249539933750401</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K36" s="0">
-        <v>1.5463917525773183</v>
+        <v>0</v>
       </c>
       <c r="L36" s="0">
-        <v>0.60025503063477692</v>
+        <v>0.14462103069697993</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>1.319287191099733</v>
+        <v>0.15014275868858901</v>
       </c>
       <c r="B37" s="0">
-        <v>1.0526315789473675</v>
+        <v>1.4035087719298234</v>
       </c>
       <c r="C37" s="0">
-        <v>1.4659075058014925</v>
+        <v>0.073548992505611213</v>
       </c>
       <c r="D37" s="0">
-        <v>1.387252662707666</v>
+        <v>0.20676556151275438</v>
       </c>
       <c r="E37" s="0">
-        <v>0.77209940630687002</v>
+        <v>0.55073242041826975</v>
       </c>
       <c r="F37" s="0">
-        <v>2.0358039515336737</v>
+        <v>0.2255940035658405</v>
       </c>
       <c r="G37" s="0">
-        <v>0.96560048280024058</v>
+        <v>0.40233353450010018</v>
       </c>
       <c r="H37" s="0">
-        <v>2.368914389592681</v>
+        <v>0.15338294608873473</v>
       </c>
       <c r="I37" s="0">
-        <v>1.8053266072173326</v>
+        <v>0.37735099600802335</v>
       </c>
       <c r="J37" s="0">
-        <v>1.1409642988590347</v>
+        <v>0.018402649981597335</v>
       </c>
       <c r="K37" s="0">
-        <v>2.9639175257731933</v>
+        <v>0</v>
       </c>
       <c r="L37" s="0">
-        <v>1.0667744844960025</v>
+        <v>0.34366933101110286</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>1.9518558629516574</v>
+        <v>0.27074923697942282</v>
       </c>
       <c r="B38" s="0">
-        <v>1.7543859649122791</v>
+        <v>1.4035087719298234</v>
       </c>
       <c r="C38" s="0">
-        <v>2.2305634106443124</v>
+        <v>0.20542994458463823</v>
       </c>
       <c r="D38" s="0">
-        <v>2.2455701680571232</v>
+        <v>0.53374365878873797</v>
       </c>
       <c r="E38" s="0">
-        <v>1.2924013246218551</v>
+        <v>0.95229571287926162</v>
       </c>
       <c r="F38" s="0">
-        <v>2.9254448204344481</v>
+        <v>0.46756176545500811</v>
       </c>
       <c r="G38" s="0">
-        <v>2.1726010863005412</v>
+        <v>0.80466706900020035</v>
       </c>
       <c r="H38" s="0">
-        <v>2.7722547293075017</v>
+        <v>0.32948929159802276</v>
       </c>
       <c r="I38" s="0">
-        <v>2.6414569720561634</v>
+        <v>0.79640920736430199</v>
       </c>
       <c r="J38" s="0">
-        <v>1.6930437983069548</v>
+        <v>0.073610599926389339</v>
       </c>
       <c r="K38" s="0">
-        <v>4.2525773195876253</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L38" s="0">
-        <v>1.7276770441327387</v>
+        <v>0.69355892140702202</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>2.7148764398936671</v>
+        <v>0.46519641626464464</v>
       </c>
       <c r="B39" s="0">
         <v>4.0350877192982422</v>
       </c>
       <c r="C39" s="0">
-        <v>2.9483001306128633</v>
+        <v>0.37408539291647086</v>
       </c>
       <c r="D39" s="0">
-        <v>3.4044190128146536</v>
+        <v>0.9424662803837176</v>
       </c>
       <c r="E39" s="0">
-        <v>1.9224917211133965</v>
+        <v>1.5406187535427654</v>
       </c>
       <c r="F39" s="0">
-        <v>3.500345668231267</v>
+        <v>0.89691809482225293</v>
       </c>
       <c r="G39" s="0">
-        <v>3.0778515389257666</v>
+        <v>1.669684168175416</v>
       </c>
       <c r="H39" s="0">
-        <v>3.800488553087539</v>
+        <v>0.76123388058853536</v>
       </c>
       <c r="I39" s="0">
-        <v>3.6503743719091939</v>
+        <v>1.3465472383865253</v>
       </c>
       <c r="J39" s="0">
-        <v>2.6131762973868211</v>
+        <v>0.20242914979757068</v>
       </c>
       <c r="K39" s="0">
-        <v>8.8917525773195809</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L39" s="0">
-        <v>2.422791030385965</v>
+        <v>1.2269461636550232</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>3.3154474746480234</v>
+        <v>0.99438810672442568</v>
       </c>
       <c r="B40" s="0">
-        <v>4.2105263157894699</v>
+        <v>3.5964912280701724</v>
       </c>
       <c r="C40" s="0">
-        <v>3.775092253262148</v>
+        <v>0.70505585919172131</v>
       </c>
       <c r="D40" s="0">
-        <v>4.4767148318226582</v>
+        <v>1.6565287428172995</v>
       </c>
       <c r="E40" s="0">
-        <v>2.5657090008651786</v>
+        <v>2.1707091500343068</v>
       </c>
       <c r="F40" s="0">
-        <v>4.1480187752428739</v>
+        <v>1.4008659898846547</v>
       </c>
       <c r="G40" s="0">
-        <v>3.4198350432508522</v>
+        <v>3.2186682760008014</v>
       </c>
       <c r="H40" s="0">
-        <v>4.3856160881667856</v>
+        <v>1.0055104243594832</v>
       </c>
       <c r="I40" s="0">
-        <v>4.117097972234907</v>
+        <v>2.1350122142559216</v>
       </c>
       <c r="J40" s="0">
-        <v>3.7173352962826613</v>
+        <v>0.31284504968715471</v>
       </c>
       <c r="K40" s="0">
-        <v>9.7938144329896826</v>
+        <v>1.0309278350515454</v>
       </c>
       <c r="L40" s="0">
-        <v>3.2936273442602526</v>
+        <v>1.8785183342145351</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>3.768337107413624</v>
+        <v>1.5654228610810352</v>
       </c>
       <c r="B41" s="0">
-        <v>7.0175438596491553</v>
+        <v>6.8421052631579267</v>
       </c>
       <c r="C41" s="0">
-        <v>4.3064203198113296</v>
+        <v>1.2769626802267398</v>
       </c>
       <c r="D41" s="0">
-        <v>5.4047556079148187</v>
+        <v>2.642271536075794</v>
       </c>
       <c r="E41" s="0">
-        <v>3.1773024254900357</v>
+        <v>2.789462692801111</v>
       </c>
       <c r="F41" s="0">
-        <v>4.333588036240605</v>
+        <v>2.1376851144343876</v>
       </c>
       <c r="G41" s="0">
-        <v>4.3250854958761016</v>
+        <v>3.1180848923757942</v>
       </c>
       <c r="H41" s="0">
-        <v>4.6696585809237279</v>
+        <v>1.8689996023405189</v>
       </c>
       <c r="I41" s="0">
-        <v>4.804273996544282</v>
+        <v>2.8341045858076437</v>
       </c>
       <c r="J41" s="0">
-        <v>4.0853882959146306</v>
+        <v>0.71770334928230006</v>
       </c>
       <c r="K41" s="0">
-        <v>10.309278350515511</v>
+        <v>1.6752577319587707</v>
       </c>
       <c r="L41" s="0">
-        <v>3.7445961496594586</v>
+        <v>2.7011476378565109</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>3.7461848971152869</v>
+        <v>2.2742935906271518</v>
       </c>
       <c r="B42" s="0">
-        <v>8.1578947368420991</v>
+        <v>8.4210526315789398</v>
       </c>
       <c r="C42" s="0">
-        <v>4.6919184874269222</v>
+        <v>2.0695164787785774</v>
       </c>
       <c r="D42" s="0">
-        <v>5.647584930156512</v>
+        <v>3.7434183636669598</v>
       </c>
       <c r="E42" s="0">
-        <v>3.6367433395984334</v>
+        <v>3.3938959992839854</v>
       </c>
       <c r="F42" s="0">
-        <v>4.208055889095073</v>
+        <v>3.0564348870210649</v>
       </c>
       <c r="G42" s="0">
-        <v>4.304968819151072</v>
+        <v>4.1842687588010428</v>
       </c>
       <c r="H42" s="0">
-        <v>4.4935522354144135</v>
+        <v>2.7438504800318104</v>
       </c>
       <c r="I42" s="0">
-        <v>4.8936466008619446</v>
+        <v>3.7596075549641488</v>
       </c>
       <c r="J42" s="0">
-        <v>5.373573794626421</v>
+        <v>1.1961722488038267</v>
       </c>
       <c r="K42" s="0">
-        <v>11.211340206185557</v>
+        <v>2.7061855670103068</v>
       </c>
       <c r="L42" s="0">
-        <v>4.3246353372935609</v>
+        <v>3.3589400678008241</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>3.9234025795018184</v>
+        <v>2.9265531160775793</v>
       </c>
       <c r="B43" s="0">
-        <v>6.4035087719298192</v>
+        <v>6.0526315789473628</v>
       </c>
       <c r="C43" s="0">
-        <v>4.6868461431161901</v>
+        <v>2.7859851126694455</v>
       </c>
       <c r="D43" s="0">
-        <v>5.8711802466761185</v>
+        <v>5.0922030149303925</v>
       </c>
       <c r="E43" s="0">
-        <v>3.8742205913064196</v>
+        <v>3.7924759091858316</v>
       </c>
       <c r="F43" s="0">
-        <v>4.0279445475384748</v>
+        <v>3.6877342357093439</v>
       </c>
       <c r="G43" s="0">
-        <v>4.9285857976262282</v>
+        <v>4.6871856769261679</v>
       </c>
       <c r="H43" s="0">
-        <v>3.7664034539567086</v>
+        <v>3.5902971084474209</v>
       </c>
       <c r="I43" s="0">
-        <v>4.6235427300351493</v>
+        <v>4.4726023316319399</v>
       </c>
       <c r="J43" s="0">
-        <v>5.0055207949944753</v>
+        <v>1.6378358483621627</v>
       </c>
       <c r="K43" s="0">
-        <v>12.113402061855659</v>
+        <v>3.0927835051546366</v>
       </c>
       <c r="L43" s="0">
-        <v>4.3308555966783784</v>
+        <v>4.0136223680527445</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>3.8027961012109839</v>
+        <v>3.6206557054248267</v>
       </c>
       <c r="B44" s="0">
-        <v>7.6315789473684141</v>
+        <v>7.1052631578947301</v>
       </c>
       <c r="C44" s="0">
-        <v>4.3508033325302078</v>
+        <v>3.4770920250066544</v>
       </c>
       <c r="D44" s="0">
-        <v>5.2124155506936214</v>
+        <v>5.4792873800879907</v>
       </c>
       <c r="E44" s="0">
-        <v>3.9171813001581159</v>
+        <v>3.8694471792117864</v>
       </c>
       <c r="F44" s="0">
-        <v>3.8605683513444644</v>
+        <v>4.0879816613906739</v>
       </c>
       <c r="G44" s="0">
-        <v>4.7475357071011821</v>
+        <v>4.8682357674512131</v>
       </c>
       <c r="H44" s="0">
-        <v>3.1812759188774611</v>
+        <v>4.3912969380219247</v>
       </c>
       <c r="I44" s="0">
-        <v>4.7665388969434526</v>
+        <v>4.6016960934241587</v>
       </c>
       <c r="J44" s="0">
-        <v>4.8030916451969041</v>
+        <v>2.20831799779168</v>
       </c>
       <c r="K44" s="0">
-        <v>8.6340206185566934</v>
+        <v>8.7628865979381363</v>
       </c>
       <c r="L44" s="0">
-        <v>4.3386309209093978</v>
+        <v>4.2266662519827039</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>3.5714285714285681</v>
+        <v>3.7781825342128545</v>
       </c>
       <c r="B45" s="0">
-        <v>5.7017543859649065</v>
+        <v>5.6140350877192935</v>
       </c>
       <c r="C45" s="0">
-        <v>4.1935606588975221</v>
+        <v>4.2493564463155726</v>
       </c>
       <c r="D45" s="0">
-        <v>4.5488423532805964</v>
+        <v>5.9144567595508803</v>
       </c>
       <c r="E45" s="0">
-        <v>3.8211163817536287</v>
+        <v>3.8974909752677554</v>
       </c>
       <c r="F45" s="0">
-        <v>3.7204817523559983</v>
+        <v>4.3226721973583633</v>
       </c>
       <c r="G45" s="0">
-        <v>3.8020519010259473</v>
+        <v>4.9889358278012423</v>
       </c>
       <c r="H45" s="0">
-        <v>2.7779355791626403</v>
+        <v>4.476509685848999</v>
       </c>
       <c r="I45" s="0">
-        <v>4.2600941391432112</v>
+        <v>4.7486643760799145</v>
       </c>
       <c r="J45" s="0">
-        <v>4.5454545454545414</v>
+        <v>3.570114096429883</v>
       </c>
       <c r="K45" s="0">
-        <v>5.4123711340206135</v>
+        <v>9.7938144329896826</v>
       </c>
       <c r="L45" s="0">
-        <v>4.0929306752091525</v>
+        <v>4.2375517059061325</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>3.2563749138525124</v>
+        <v>3.8175642414098618</v>
       </c>
       <c r="B46" s="0">
-        <v>4.122807017543856</v>
+        <v>4.3859649122806976</v>
       </c>
       <c r="C46" s="0">
-        <v>3.9019008610304433</v>
+        <v>4.5879354290569205</v>
       </c>
       <c r="D46" s="0">
-        <v>3.7987161301180454</v>
+        <v>5.6980741951770684</v>
       </c>
       <c r="E46" s="0">
-        <v>3.7310182284674331</v>
+        <v>3.8264864703600909</v>
       </c>
       <c r="F46" s="0">
-        <v>3.4930684423097884</v>
+        <v>4.2025979696539642</v>
       </c>
       <c r="G46" s="0">
-        <v>2.8163347415007016</v>
+        <v>3.7819352243009421</v>
       </c>
       <c r="H46" s="0">
-        <v>2.7097653809009805</v>
+        <v>4.4310628870078927</v>
       </c>
       <c r="I46" s="0">
-        <v>4.1250422037298131</v>
+        <v>4.7268177394689239</v>
       </c>
       <c r="J46" s="0">
-        <v>3.6253220463746749</v>
+        <v>4.490246595509749</v>
       </c>
       <c r="K46" s="0">
-        <v>3.7371134020618522</v>
+        <v>10.824742268041227</v>
       </c>
       <c r="L46" s="0">
-        <v>3.8643361428171521</v>
+        <v>4.1535782042111116</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>3.4434380230383144</v>
+        <v>3.903711725903336</v>
       </c>
       <c r="B47" s="0">
-        <v>2.4561403508772046</v>
+        <v>2.5438596491228189</v>
       </c>
       <c r="C47" s="0">
-        <v>3.8067944052042431</v>
+        <v>4.6373907860865806</v>
       </c>
       <c r="D47" s="0">
-        <v>3.0942706705455389</v>
+        <v>4.8950544562787242</v>
       </c>
       <c r="E47" s="0">
-        <v>3.6677705182135676</v>
+        <v>3.5860258360929786</v>
       </c>
       <c r="F47" s="0">
-        <v>3.2256303896954632</v>
+        <v>4.0315831604992365</v>
       </c>
       <c r="G47" s="0">
-        <v>3.3393683363508506</v>
+        <v>2.9772681553007585</v>
       </c>
       <c r="H47" s="0">
-        <v>2.3518718400272789</v>
+        <v>3.8629779014940815</v>
       </c>
       <c r="I47" s="0">
-        <v>4.0297114257909659</v>
+        <v>4.669222061130883</v>
       </c>
       <c r="J47" s="0">
-        <v>3.0548398969451744</v>
+        <v>5.0607287449392944</v>
       </c>
       <c r="K47" s="0">
-        <v>1.8041237113402144</v>
+        <v>11.082474226804175</v>
       </c>
       <c r="L47" s="0">
-        <v>3.5564333032687627</v>
+        <v>3.991851460205909</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>3.4458993797381088</v>
+        <v>3.6083489219257623</v>
       </c>
       <c r="B48" s="0">
-        <v>1.1403508771929816</v>
+        <v>1.4912280701754372</v>
       </c>
       <c r="C48" s="0">
-        <v>3.5798069972989737</v>
+        <v>4.4776119402985035</v>
       </c>
       <c r="D48" s="0">
-        <v>2.8225903397206236</v>
+        <v>4.1641622388382622</v>
       </c>
       <c r="E48" s="0">
-        <v>3.4863808586174976</v>
+        <v>3.5997493958650284</v>
       </c>
       <c r="F48" s="0">
-        <v>3.2365462285776636</v>
+        <v>3.9206054651966635</v>
       </c>
       <c r="G48" s="0">
-        <v>2.5950512975256466</v>
+        <v>2.8968014484007214</v>
       </c>
       <c r="H48" s="0">
-        <v>2.6643185820598738</v>
+        <v>3.3460205646764725</v>
       </c>
       <c r="I48" s="0">
-        <v>3.640444082540562</v>
+        <v>4.3037874123651925</v>
       </c>
       <c r="J48" s="0">
-        <v>2.4107471475892508</v>
+        <v>5.1343393448656558</v>
       </c>
       <c r="K48" s="0">
-        <v>1.417525773195875</v>
+        <v>13.144329896907205</v>
       </c>
       <c r="L48" s="0">
-        <v>3.4569091531116816</v>
+        <v>3.8052436786613972</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>3.1751501427586857</v>
+        <v>3.509894653933245</v>
       </c>
       <c r="B49" s="0">
-        <v>1.3157894736842093</v>
+        <v>2.0175438596491211</v>
       </c>
       <c r="C49" s="0">
-        <v>3.3236536096070175</v>
+        <v>4.3089564919666712</v>
       </c>
       <c r="D49" s="0">
-        <v>2.9956963912196737</v>
+        <v>3.4308657706825638</v>
       </c>
       <c r="E49" s="0">
-        <v>3.3139413466988841</v>
+        <v>3.4064262060323962</v>
       </c>
       <c r="F49" s="0">
-        <v>2.861769093621509</v>
+        <v>3.6131426700141871</v>
       </c>
       <c r="G49" s="0">
-        <v>2.5145845906256263</v>
+        <v>2.4542345604506113</v>
       </c>
       <c r="H49" s="0">
-        <v>2.9426802249616517</v>
+        <v>3.0733397716298327</v>
       </c>
       <c r="I49" s="0">
-        <v>3.3107584755019737</v>
+        <v>4.1488748982145305</v>
       </c>
       <c r="J49" s="0">
-        <v>2.0794994479204987</v>
+        <v>5.1711446448288507</v>
       </c>
       <c r="K49" s="0">
-        <v>0.12886597938144317</v>
+        <v>7.6030927835051472</v>
       </c>
       <c r="L49" s="0">
-        <v>3.3496096787236</v>
+        <v>3.5797592759618042</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>3.0594663778674778</v>
+        <v>3.4286698828394182</v>
       </c>
       <c r="B50" s="0">
         <v>0.96491228070175361</v>
       </c>
       <c r="C50" s="0">
-        <v>3.1309045257992087</v>
+        <v>4.0718243954399584</v>
       </c>
       <c r="D50" s="0">
-        <v>3.1255259298439615</v>
+        <v>2.9788666362128216</v>
       </c>
       <c r="E50" s="0">
-        <v>3.2393567827202459</v>
+        <v>3.2942510218085239</v>
       </c>
       <c r="F50" s="0">
-        <v>2.8435760288178122</v>
+        <v>3.5203580395153336</v>
       </c>
       <c r="G50" s="0">
-        <v>2.6151679742506517</v>
+        <v>2.8766847716757167</v>
       </c>
       <c r="H50" s="0">
-        <v>2.8006589785831935</v>
+        <v>2.4654888371300325</v>
       </c>
       <c r="I50" s="0">
-        <v>3.1697483664673958</v>
+        <v>3.8867152588826408</v>
       </c>
       <c r="J50" s="0">
-        <v>2.1347073978652906</v>
+        <v>4.2510121457489838</v>
       </c>
       <c r="K50" s="0">
-        <v>0.5154639175257727</v>
+        <v>5.5412371134020564</v>
       </c>
       <c r="L50" s="0">
-        <v>3.1956582589493951</v>
+        <v>3.5222218766522535</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>2.7764103573889902</v>
+        <v>3.1259230087624266</v>
       </c>
       <c r="B51" s="0">
-        <v>0.70175438596491169</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C51" s="0">
-        <v>2.8950405153501797</v>
+        <v>3.7433901013200748</v>
       </c>
       <c r="D51" s="0">
-        <v>3.3322914913567159</v>
+        <v>2.8851008583175028</v>
       </c>
       <c r="E51" s="0">
-        <v>3.0293266505563983</v>
+        <v>3.1659655717652648</v>
       </c>
       <c r="F51" s="0">
-        <v>2.6088854928501233</v>
+        <v>3.2365462285776636</v>
       </c>
       <c r="G51" s="0">
-        <v>3.4198350432508522</v>
+        <v>2.3938845302755962</v>
       </c>
       <c r="H51" s="0">
-        <v>3.1415099698914926</v>
+        <v>2.6075100835084903</v>
       </c>
       <c r="I51" s="0">
-        <v>3.0108637365692812</v>
+        <v>3.5053921471271643</v>
       </c>
       <c r="J51" s="0">
-        <v>2.2267206477732771</v>
+        <v>3.7909458962090508</v>
       </c>
       <c r="K51" s="0">
-        <v>0</v>
+        <v>3.7371134020618522</v>
       </c>
       <c r="L51" s="0">
-        <v>3.0681429415606605</v>
+        <v>3.3122881224147021</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>2.8010239243871196</v>
+        <v>3.199763709756815</v>
       </c>
       <c r="B52" s="0">
         <v>0.78947368421052566</v>
       </c>
       <c r="C52" s="0">
-        <v>2.9178660647484724</v>
+        <v>3.7370496709316594</v>
       </c>
       <c r="D52" s="0">
-        <v>3.505397542855766</v>
+        <v>3.1062919241218445</v>
       </c>
       <c r="E52" s="0">
-        <v>2.9666756168143418</v>
+        <v>3.0084429726423791</v>
       </c>
       <c r="F52" s="0">
-        <v>2.6216206382127112</v>
+        <v>3.043699741658477</v>
       </c>
       <c r="G52" s="0">
-        <v>3.399718366525847</v>
+        <v>3.1985515992757963</v>
       </c>
       <c r="H52" s="0">
-        <v>2.9029142759756832</v>
+        <v>2.4995739362608624</v>
       </c>
       <c r="I52" s="0">
-        <v>2.8221882385652695</v>
+        <v>3.3425354014815962</v>
       </c>
       <c r="J52" s="0">
-        <v>2.5763709974236271</v>
+        <v>3.1836584468163389</v>
       </c>
       <c r="K52" s="0">
-        <v>0</v>
+        <v>2.1907216494845341</v>
       </c>
       <c r="L52" s="0">
-        <v>2.9421826890181295</v>
+        <v>3.2143190371038446</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>2.6828788027960986</v>
+        <v>3.1505365757605563</v>
       </c>
       <c r="B53" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C53" s="0">
-        <v>2.7377978417174935</v>
+        <v>3.4770920250066544</v>
       </c>
       <c r="D53" s="0">
-        <v>3.4236530185367697</v>
+        <v>3.0846536676844632</v>
       </c>
       <c r="E53" s="0">
-        <v>2.8192965183925511</v>
+        <v>2.9302783495927658</v>
       </c>
       <c r="F53" s="0">
-        <v>2.57068005676236</v>
+        <v>2.9672888694829505</v>
       </c>
       <c r="G53" s="0">
-        <v>2.9169181251257266</v>
+        <v>3.2589016294508117</v>
       </c>
       <c r="H53" s="0">
-        <v>2.7665738794523635</v>
+        <v>2.7552121797420872</v>
       </c>
       <c r="I53" s="0">
-        <v>2.7407598657424854</v>
+        <v>3.1220829774979615</v>
       </c>
       <c r="J53" s="0">
-        <v>2.9444239970555737</v>
+        <v>2.0058888479941093</v>
       </c>
       <c r="K53" s="0">
-        <v>0</v>
+        <v>1.5463917525773183</v>
       </c>
       <c r="L53" s="0">
-        <v>2.7742356856280881</v>
+        <v>3.0323764500979666</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>2.6828788027960986</v>
+        <v>3.1013094417642977</v>
       </c>
       <c r="B54" s="0">
-        <v>0.43859649122806976</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C54" s="0">
-        <v>2.6464956441243208</v>
+        <v>3.198113087916405</v>
       </c>
       <c r="D54" s="0">
-        <v>3.2793979756208951</v>
+        <v>3.5390570528694698</v>
       </c>
       <c r="E54" s="0">
-        <v>2.7739491034935386</v>
+        <v>2.8270533130463291</v>
       </c>
       <c r="F54" s="0">
-        <v>2.3760142633628041</v>
+        <v>2.7780809955245034</v>
       </c>
       <c r="G54" s="0">
-        <v>2.4542345604506113</v>
+        <v>2.9169181251257266</v>
       </c>
       <c r="H54" s="0">
-        <v>2.5677441345225223</v>
+        <v>2.8631483269897151</v>
       </c>
       <c r="I54" s="0">
-        <v>2.5500983098647469</v>
+        <v>2.9016305535143268</v>
       </c>
       <c r="J54" s="0">
-        <v>2.8892160471107813</v>
+        <v>2.0794994479204987</v>
       </c>
       <c r="K54" s="0">
-        <v>0</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L54" s="0">
-        <v>2.539420893851271</v>
+        <v>2.8504338630920882</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>2.6041153884020849</v>
+        <v>2.783794427488429</v>
       </c>
       <c r="B55" s="0">
-        <v>0.78947368421052566</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C55" s="0">
-        <v>2.4233124944521212</v>
+        <v>3.0992023738571346</v>
       </c>
       <c r="D55" s="0">
-        <v>2.7769095761305964</v>
+        <v>3.5703123121679097</v>
       </c>
       <c r="E55" s="0">
-        <v>2.6671440078761277</v>
+        <v>2.7011545690503871</v>
       </c>
       <c r="F55" s="0">
-        <v>2.2686751810209929</v>
+        <v>2.5979696539679051</v>
       </c>
       <c r="G55" s="0">
-        <v>2.1323677328505313</v>
+        <v>2.9169181251257266</v>
       </c>
       <c r="H55" s="0">
-        <v>2.0621484974152113</v>
+        <v>3.0960631710503863</v>
       </c>
       <c r="I55" s="0">
-        <v>2.3415622331234709</v>
+        <v>2.8122579491966371</v>
       </c>
       <c r="J55" s="0">
-        <v>2.7235921972764054</v>
+        <v>2.0242914979757067</v>
       </c>
       <c r="K55" s="0">
-        <v>0</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L55" s="0">
-        <v>2.5254253102354345</v>
+        <v>2.6576058221627816</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>2.5671950379048907</v>
+        <v>2.7690262872895515</v>
       </c>
       <c r="B56" s="0">
-        <v>0.87719298245613953</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C56" s="0">
-        <v>2.3472273297911439</v>
+        <v>2.8138830063784708</v>
       </c>
       <c r="D56" s="0">
-        <v>2.2503786694876524</v>
+        <v>3.3803765056620074</v>
       </c>
       <c r="E56" s="0">
-        <v>2.5865926787791977</v>
+        <v>2.7339717772009879</v>
       </c>
       <c r="F56" s="0">
-        <v>2.0740093876214369</v>
+        <v>2.5579449113997721</v>
       </c>
       <c r="G56" s="0">
-        <v>2.2128344397505515</v>
+        <v>2.6554013277006616</v>
       </c>
       <c r="H56" s="0">
-        <v>1.8121911037891252</v>
+        <v>3.1358291200363548</v>
       </c>
       <c r="I56" s="0">
-        <v>2.2025381819626206</v>
+        <v>2.7010387082679563</v>
       </c>
       <c r="J56" s="0">
-        <v>2.8156054471843919</v>
+        <v>2.2819285977180694</v>
       </c>
       <c r="K56" s="0">
         <v>0</v>
       </c>
       <c r="L56" s="0">
-        <v>2.3590333716915977</v>
+        <v>2.5316455696202507</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>2.3481342916215659</v>
+        <v>2.8330215614847196</v>
       </c>
       <c r="B57" s="0">
-        <v>1.5789473684210689</v>
+        <v>1.4912280701754539</v>
       </c>
       <c r="C57" s="0">
-        <v>2.1988612587022631</v>
+        <v>2.7809127683587445</v>
       </c>
       <c r="D57" s="0">
-        <v>2.0051450965306867</v>
+        <v>3.1183131776982021</v>
       </c>
       <c r="E57" s="0">
-        <v>2.5478087055103336</v>
+        <v>2.5531787941167958</v>
       </c>
       <c r="F57" s="0">
-        <v>2.0958410653858963</v>
+        <v>2.4706182003420549</v>
       </c>
       <c r="G57" s="0">
-        <v>1.7300341983504499</v>
+        <v>2.0116676725005234</v>
       </c>
       <c r="H57" s="0">
-        <v>1.7440209055274847</v>
+        <v>2.9142759756859924</v>
       </c>
       <c r="I57" s="0">
-        <v>2.0794025937916043</v>
+        <v>2.4309348374411881</v>
       </c>
       <c r="J57" s="0">
-        <v>1.8218623481781562</v>
+        <v>3.1836584468163744</v>
       </c>
       <c r="K57" s="0">
         <v>0</v>
       </c>
       <c r="L57" s="0">
-        <v>2.2843902590738265</v>
+        <v>2.5238702453892588</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>2.3456729349217267</v>
+        <v>2.5967313183026461</v>
       </c>
       <c r="B58" s="0">
-        <v>2.1929824561403488</v>
+        <v>1.9298245614035072</v>
       </c>
       <c r="C58" s="0">
-        <v>2.0999505446429687</v>
+        <v>2.5767509098517585</v>
       </c>
       <c r="D58" s="0">
-        <v>1.6228692328035952</v>
+        <v>2.4811867381530521</v>
       </c>
       <c r="E58" s="0">
-        <v>2.4129598138369261</v>
+        <v>2.4374235508219195</v>
       </c>
       <c r="F58" s="0">
-        <v>1.9593930793581471</v>
+        <v>2.3032420041480166</v>
       </c>
       <c r="G58" s="0">
-        <v>1.991550995775496</v>
+        <v>2.253067793200561</v>
       </c>
       <c r="H58" s="0">
-        <v>1.7099358063966354</v>
+        <v>2.4484462875646176</v>
       </c>
       <c r="I58" s="0">
-        <v>1.9264761375146453</v>
+        <v>2.1826776032253563</v>
       </c>
       <c r="J58" s="0">
-        <v>1.9322782480677201</v>
+        <v>2.9996319470003656</v>
       </c>
       <c r="K58" s="0">
         <v>0</v>
       </c>
       <c r="L58" s="0">
-        <v>2.0962274126831071</v>
+        <v>2.2221876652256381</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>2.1413803288372533</v>
+        <v>2.6951855862951635</v>
       </c>
       <c r="B59" s="0">
-        <v>2.0175438596491211</v>
+        <v>2.2807017543859631</v>
       </c>
       <c r="C59" s="0">
-        <v>1.9274908380780869</v>
+        <v>2.4017550311315112</v>
       </c>
       <c r="D59" s="0">
-        <v>1.7454860192820891</v>
+        <v>2.0844853701343959</v>
       </c>
       <c r="E59" s="0">
-        <v>2.3013813061248825</v>
+        <v>2.3127181598496351</v>
       </c>
       <c r="F59" s="0">
-        <v>1.861150529418184</v>
+        <v>2.2068187606884235</v>
       </c>
       <c r="G59" s="0">
-        <v>1.8708509354254659</v>
+        <v>1.7501508750754358</v>
       </c>
       <c r="H59" s="0">
-        <v>1.880361302050785</v>
+        <v>2.2098505936488082</v>
       </c>
       <c r="I59" s="0">
-        <v>1.8768246906714845</v>
+        <v>2.2323290500685169</v>
       </c>
       <c r="J59" s="0">
-        <v>1.7666543982333442</v>
+        <v>3.1652557968347415</v>
       </c>
       <c r="K59" s="0">
         <v>0</v>
       </c>
       <c r="L59" s="0">
-        <v>1.9360557335240864</v>
+        <v>2.1802009143781276</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>2.2053756030323894</v>
+        <v>2.5475041843063875</v>
       </c>
       <c r="B60" s="0">
-        <v>2.2807017543859631</v>
+        <v>2.8947368421052606</v>
       </c>
       <c r="C60" s="0">
-        <v>1.8590141898832078</v>
+        <v>2.3370826411696806</v>
       </c>
       <c r="D60" s="0">
-        <v>1.7454860192820891</v>
+        <v>1.9474430793643145</v>
       </c>
       <c r="E60" s="0">
-        <v>2.2172499179569773</v>
+        <v>2.2411169784301421</v>
       </c>
       <c r="F60" s="0">
-        <v>1.7465342211548942</v>
+        <v>2.2832296328639505</v>
       </c>
       <c r="G60" s="0">
-        <v>2.3134178233755764</v>
+        <v>1.7903842285254461</v>
       </c>
       <c r="H60" s="0">
-        <v>2.1757654945179783</v>
+        <v>2.0848718968357649</v>
       </c>
       <c r="I60" s="0">
-        <v>1.7278703501420014</v>
+        <v>2.0376953784433258</v>
       </c>
       <c r="J60" s="0">
-        <v>1.7482517482517468</v>
+        <v>2.705189547294808</v>
       </c>
       <c r="K60" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L60" s="0">
-        <v>1.8225359997511881</v>
+        <v>2.1584300065312707</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>2.1512257556365051</v>
+        <v>2.237373240129958</v>
       </c>
       <c r="B61" s="0">
-        <v>3.3333333333333304</v>
+        <v>2.7192982456140329</v>
       </c>
       <c r="C61" s="0">
-        <v>1.7677119922900351</v>
+        <v>2.2229548941782147</v>
       </c>
       <c r="D61" s="0">
-        <v>1.7599115235736766</v>
+        <v>1.670954247108887</v>
       </c>
       <c r="E61" s="0">
-        <v>2.1701124735224777</v>
+        <v>2.2679674214624521</v>
       </c>
       <c r="F61" s="0">
-        <v>1.7483535276352637</v>
+        <v>2.0339846450533039</v>
       </c>
       <c r="G61" s="0">
-        <v>2.5347012673506315</v>
+        <v>1.7702675518004409</v>
       </c>
       <c r="H61" s="0">
-        <v>2.0167016985741051</v>
+        <v>1.6701698574106672</v>
       </c>
       <c r="I61" s="0">
-        <v>1.5233063891481784</v>
+        <v>1.9681833528629007</v>
       </c>
       <c r="J61" s="0">
-        <v>2.0058888479941093</v>
+        <v>2.6315789473684186</v>
       </c>
       <c r="K61" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L61" s="0">
-        <v>1.7649986004416367</v>
+        <v>1.9656019656019639</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>2.0429260608447359</v>
+        <v>2.2546027370286481</v>
       </c>
       <c r="B62" s="0">
-        <v>2.7192982456140329</v>
+        <v>3.7719298245614001</v>
       </c>
       <c r="C62" s="0">
-        <v>1.7233289795711317</v>
+        <v>2.008648347049796</v>
       </c>
       <c r="D62" s="0">
-        <v>1.7454860192820891</v>
+        <v>1.7190392614141787</v>
       </c>
       <c r="E62" s="0">
-        <v>2.1008979981503009</v>
+        <v>2.2005429756257624</v>
       </c>
       <c r="F62" s="0">
-        <v>1.6319179128916044</v>
+        <v>2.0103336608084979</v>
       </c>
       <c r="G62" s="0">
-        <v>1.7099175216254261</v>
+        <v>2.2329511164755562</v>
       </c>
       <c r="H62" s="0">
-        <v>1.9258081008918917</v>
+        <v>1.6758507072658055</v>
       </c>
       <c r="I62" s="0">
-        <v>1.5431669678854427</v>
+        <v>1.8410756489444087</v>
       </c>
       <c r="J62" s="0">
-        <v>1.7114464482885521</v>
+        <v>1.7666543982333443</v>
       </c>
       <c r="K62" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L62" s="0">
-        <v>1.7245669144403306</v>
+        <v>1.8862936584455554</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>1.8263266712611974</v>
+        <v>2.22260509993108</v>
       </c>
       <c r="B63" s="0">
-        <v>2.5438596491228047</v>
+        <v>2.9824561403508745</v>
       </c>
       <c r="C63" s="0">
-        <v>1.582571424948324</v>
+        <v>2.0847335117107728</v>
       </c>
       <c r="D63" s="0">
-        <v>1.5868054720746263</v>
+        <v>1.7671242757194705</v>
       </c>
       <c r="E63" s="0">
-        <v>1.9839494018317951</v>
+        <v>2.0889644679137187</v>
       </c>
       <c r="F63" s="0">
-        <v>1.6246406869701255</v>
+        <v>1.9266455627114929</v>
       </c>
       <c r="G63" s="0">
-        <v>1.810500905250451</v>
+        <v>2.1726010863005412</v>
       </c>
       <c r="H63" s="0">
-        <v>1.8917230017610618</v>
+        <v>1.9769357495881366</v>
       </c>
       <c r="I63" s="0">
-        <v>1.3842823379873277</v>
+        <v>1.6265813985819533</v>
       </c>
       <c r="J63" s="0">
-        <v>1.6378358483621627</v>
+        <v>1.5826278984173707</v>
       </c>
       <c r="K63" s="0">
-        <v>0.64432989690721587</v>
+        <v>0</v>
       </c>
       <c r="L63" s="0">
-        <v>1.6981308120548613</v>
+        <v>1.7587783410568205</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>1.7623313970660615</v>
+        <v>2.2152210298316413</v>
       </c>
       <c r="B64" s="0">
-        <v>2.6315789473684186</v>
+        <v>2.1929824561403488</v>
       </c>
       <c r="C64" s="0">
-        <v>1.5749629084822265</v>
+        <v>1.8780354810484519</v>
       </c>
       <c r="D64" s="0">
-        <v>1.5218907027624826</v>
+        <v>1.7575072728584122</v>
       </c>
       <c r="E64" s="0">
-        <v>1.9260717801843714</v>
+        <v>1.9511321936811938</v>
       </c>
       <c r="F64" s="0">
-        <v>1.4699996361387027</v>
+        <v>1.7720045118800696</v>
       </c>
       <c r="G64" s="0">
-        <v>1.6495674914504108</v>
+        <v>1.7300341983504308</v>
       </c>
       <c r="H64" s="0">
-        <v>1.6076805090041457</v>
+        <v>1.9428506504573066</v>
       </c>
       <c r="I64" s="0">
-        <v>1.2671049234374678</v>
+        <v>1.5689857202438866</v>
       </c>
       <c r="J64" s="0">
-        <v>1.8954729481045254</v>
+        <v>1.6746411483253574</v>
       </c>
       <c r="K64" s="0">
-        <v>0.5154639175257727</v>
+        <v>0</v>
       </c>
       <c r="L64" s="0">
-        <v>1.5364040680496363</v>
+        <v>1.5846110782819629</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>1.6786452692724214</v>
+        <v>2.0133897804469809</v>
       </c>
       <c r="B65" s="0">
-        <v>2.9824561403508745</v>
+        <v>2.368421052631577</v>
       </c>
       <c r="C65" s="0">
-        <v>1.4151840626941743</v>
+        <v>1.8082907467758895</v>
       </c>
       <c r="D65" s="0">
-        <v>1.2333806169307324</v>
+        <v>1.6925925035462681</v>
       </c>
       <c r="E65" s="0">
-        <v>1.8514872162057325</v>
+        <v>1.8974313076165741</v>
       </c>
       <c r="F65" s="0">
-        <v>1.4536258778153754</v>
+        <v>1.6482916712149314</v>
       </c>
       <c r="G65" s="0">
-        <v>1.3880506940253456</v>
+        <v>1.669684168175416</v>
       </c>
       <c r="H65" s="0">
-        <v>1.3690848150883359</v>
+        <v>2.0848718968357649</v>
       </c>
       <c r="I65" s="0">
-        <v>1.2234116502154861</v>
+        <v>1.308812138785723</v>
       </c>
       <c r="J65" s="0">
         <v>1.5090172984909813</v>
       </c>
       <c r="K65" s="0">
-        <v>1.1597938144329887</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L65" s="0">
-        <v>1.349796286505146</v>
+        <v>1.6732497745155959</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>1.6121886383774722</v>
+        <v>1.9149355124544631</v>
       </c>
       <c r="B66" s="0">
-        <v>0.87719298245613953</v>
+        <v>1.4912280701754372</v>
       </c>
       <c r="C66" s="0">
-        <v>1.3086648321688066</v>
+        <v>1.7550311315132057</v>
       </c>
       <c r="D66" s="0">
-        <v>1.120380833313297</v>
+        <v>1.5988267256509494</v>
       </c>
       <c r="E66" s="0">
-        <v>1.8312002148035427</v>
+        <v>1.7595990333840494</v>
       </c>
       <c r="F66" s="0">
-        <v>1.4354328130116787</v>
+        <v>1.6519302841756709</v>
       </c>
       <c r="G66" s="0">
-        <v>1.2070006035003007</v>
+        <v>1.7300341983504308</v>
       </c>
       <c r="H66" s="0">
-        <v>1.1986593194341861</v>
+        <v>1.8917230017610618</v>
       </c>
       <c r="I66" s="0">
-        <v>1.1121924092868056</v>
+        <v>1.4061289745983185</v>
       </c>
       <c r="J66" s="0">
-        <v>1.2697828487302161</v>
+        <v>1.4354066985645921</v>
       </c>
       <c r="K66" s="0">
-        <v>0.64432989690721587</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L66" s="0">
-        <v>1.3280253786582887</v>
+        <v>1.5659503001275137</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>1.4103573889928116</v>
+        <v>1.8312493846608236</v>
       </c>
       <c r="B67" s="0">
-        <v>2.0175438596491211</v>
+        <v>1.2280701754385954</v>
       </c>
       <c r="C67" s="0">
-        <v>1.2858392827705134</v>
+        <v>1.582571424948324</v>
       </c>
       <c r="D67" s="0">
-        <v>0.9424662803837176</v>
+        <v>1.3824441612771368</v>
       </c>
       <c r="E67" s="0">
-        <v>1.683821116381752</v>
+        <v>1.7154449715086948</v>
       </c>
       <c r="F67" s="0">
-        <v>1.2880689881017346</v>
+        <v>1.6446530582541921</v>
       </c>
       <c r="G67" s="0">
-        <v>1.0863005431502706</v>
+        <v>1.0460671897002607</v>
       </c>
       <c r="H67" s="0">
-        <v>1.3065954666818145</v>
+        <v>1.9769357495881366</v>
       </c>
       <c r="I67" s="0">
-        <v>1.0724712518122768</v>
+        <v>1.3822962801136012</v>
       </c>
       <c r="J67" s="0">
-        <v>1.2513801987486188</v>
+        <v>1.7666543982333443</v>
       </c>
       <c r="K67" s="0">
-        <v>0.5154639175257727</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L67" s="0">
-        <v>1.3233601841196767</v>
+        <v>1.4524305663546158</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>1.3463621147976752</v>
+        <v>1.7155656197696154</v>
       </c>
       <c r="B68" s="0">
-        <v>0.61403508771929771</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C68" s="0">
-        <v>1.1400093838369738</v>
+        <v>1.5001458298989323</v>
       </c>
       <c r="D68" s="0">
-        <v>0.783785733176255</v>
+        <v>1.178082850479647</v>
       </c>
       <c r="E68" s="0">
-        <v>1.5871595214654362</v>
+        <v>1.6414570840418852</v>
       </c>
       <c r="F68" s="0">
-        <v>1.2134774224065774</v>
+        <v>1.4190590546883515</v>
       </c>
       <c r="G68" s="0">
-        <v>1.3075839871253259</v>
+        <v>1.1667672500502908</v>
       </c>
       <c r="H68" s="0">
-        <v>1.2781912174061227</v>
+        <v>1.7610634550928805</v>
       </c>
       <c r="I68" s="0">
-        <v>1.0684991360648239</v>
+        <v>1.1717741454985988</v>
       </c>
       <c r="J68" s="0">
-        <v>1.3065881486934106</v>
+        <v>1.9506808980493173</v>
       </c>
       <c r="K68" s="0">
         <v>0.5154639175257727</v>
       </c>
       <c r="L68" s="0">
-        <v>1.2564923957329008</v>
+        <v>1.4135539451995136</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>1.2922122674018051</v>
+        <v>1.6491089888746846</v>
       </c>
       <c r="B69" s="0">
-        <v>0.43859649122807465</v>
+        <v>0.70175438596491946</v>
       </c>
       <c r="C69" s="0">
-        <v>1.1121114901279612</v>
+        <v>1.5014139159766318</v>
       </c>
       <c r="D69" s="0">
-        <v>0.75012622316255906</v>
+        <v>1.0747000697232816</v>
       </c>
       <c r="E69" s="0">
-        <v>1.4606641009576806</v>
+        <v>1.5901429040245991</v>
       </c>
       <c r="F69" s="0">
-        <v>1.2262125677691789</v>
+        <v>1.4463486518939128</v>
       </c>
       <c r="G69" s="0">
-        <v>1.8105009052504712</v>
+        <v>1.5691007845504084</v>
       </c>
       <c r="H69" s="0">
-        <v>1.1645742203033693</v>
+        <v>1.556552860307918</v>
       </c>
       <c r="I69" s="0">
-        <v>0.88379575380827502</v>
+        <v>1.0843875990546477</v>
       </c>
       <c r="J69" s="0">
-        <v>0.90172984909827925</v>
+        <v>1.6010305483989857</v>
       </c>
       <c r="K69" s="0">
-        <v>0.51546391752577847</v>
+        <v>0.90206185567011221</v>
       </c>
       <c r="L69" s="0">
-        <v>1.2176157745778122</v>
+        <v>1.258047460579119</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>1.2232942798070285</v>
+        <v>1.5137343703849549</v>
       </c>
       <c r="B70" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.35087719298245584</v>
       </c>
       <c r="C70" s="0">
-        <v>1.0626561330983137</v>
+        <v>1.2896435410035623</v>
       </c>
       <c r="D70" s="0">
-        <v>0.82225374462048839</v>
+        <v>0.82946649676628215</v>
       </c>
       <c r="E70" s="0">
-        <v>1.367582565112323</v>
+        <v>1.4517139532802279</v>
       </c>
       <c r="F70" s="0">
-        <v>1.1552596150347478</v>
+        <v>1.4208783611687212</v>
       </c>
       <c r="G70" s="0">
-        <v>1.2271172802253056</v>
+        <v>1.3277006638503308</v>
       </c>
       <c r="H70" s="0">
-        <v>1.2157018689996013</v>
+        <v>1.2838720672612611</v>
       </c>
       <c r="I70" s="0">
-        <v>0.90564239041925609</v>
+        <v>1.0744573096860033</v>
       </c>
       <c r="J70" s="0">
-        <v>1.0305483989694506</v>
+        <v>1.6378358483621627</v>
       </c>
       <c r="K70" s="0">
-        <v>0</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L70" s="0">
-        <v>1.1305321431903701</v>
+        <v>1.3155848598886562</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>1.1199172984148853</v>
+        <v>1.4103573889928116</v>
       </c>
       <c r="B71" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C71" s="0">
-        <v>0.99671565705880039</v>
+        <v>1.3657287056645393</v>
       </c>
       <c r="D71" s="0">
-        <v>0.74772197244728611</v>
+        <v>0.78618998389151951</v>
       </c>
       <c r="E71" s="0">
-        <v>1.2822578239207603</v>
+        <v>1.3419254751036713</v>
       </c>
       <c r="F71" s="0">
-        <v>1.0097150966051733</v>
+        <v>1.222573954808426</v>
       </c>
       <c r="G71" s="0">
-        <v>1.2271172802253056</v>
+        <v>1.2472339569503106</v>
       </c>
       <c r="H71" s="0">
-        <v>1.2781912174061227</v>
+        <v>1.4486167130602725</v>
       </c>
       <c r="I71" s="0">
-        <v>0.83811642271255715</v>
+        <v>0.97912653174713427</v>
       </c>
       <c r="J71" s="0">
-        <v>0.92013249907986661</v>
+        <v>1.601030548398968</v>
       </c>
       <c r="K71" s="0">
-        <v>0</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L71" s="0">
-        <v>1.0776599384194312</v>
+        <v>1.1709638291916764</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>0.96977453972629624</v>
+        <v>1.3439007580978624</v>
       </c>
       <c r="B72" s="0">
         <v>0.17543859649122792</v>
       </c>
       <c r="C72" s="0">
-        <v>1.0017880013695319</v>
+        <v>1.1793200522451455</v>
       </c>
       <c r="D72" s="0">
-        <v>0.60827543096194026</v>
+        <v>0.75253047387781535</v>
       </c>
       <c r="E72" s="0">
-        <v>1.1539723738775014</v>
+        <v>1.2607774694949123</v>
       </c>
       <c r="F72" s="0">
-        <v>1.0188116290070217</v>
+        <v>1.3208165047483889</v>
       </c>
       <c r="G72" s="0">
-        <v>1.0863005431502706</v>
+        <v>1.1466505733252856</v>
       </c>
       <c r="H72" s="0">
-        <v>1.1077657217519732</v>
+        <v>1.2838720672612611</v>
       </c>
       <c r="I72" s="0">
-        <v>0.79640920736430199</v>
+        <v>0.94536354789378485</v>
       </c>
       <c r="J72" s="0">
-        <v>1.1961722488038267</v>
+        <v>1.5642252484357733</v>
       </c>
       <c r="K72" s="0">
-        <v>0</v>
+        <v>0.64432989690721587</v>
       </c>
       <c r="L72" s="0">
-        <v>1.003016825801635</v>
+        <v>1.1056511056511047</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>0.93531554592891519</v>
+        <v>1.2922122674017909</v>
       </c>
       <c r="B73" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C73" s="0">
-        <v>0.89019642653343234</v>
+        <v>1.1159157483609978</v>
       </c>
       <c r="D73" s="0">
-        <v>0.60106267881614639</v>
+        <v>0.74772197244728611</v>
       </c>
       <c r="E73" s="0">
-        <v>1.1044482233956852</v>
+        <v>1.1157850771204381</v>
       </c>
       <c r="F73" s="0">
-        <v>0.92056907906705876</v>
+        <v>1.1661754539169658</v>
       </c>
       <c r="G73" s="0">
-        <v>1.0863005431502706</v>
+        <v>1.1064172198752757</v>
       </c>
       <c r="H73" s="0">
-        <v>1.0509572232005899</v>
+        <v>1.2554678179855696</v>
       </c>
       <c r="I73" s="0">
-        <v>0.65738515620345117</v>
+        <v>0.84010248058628356</v>
       </c>
       <c r="J73" s="0">
-        <v>1.10415899889584</v>
+        <v>1.3617960986382027</v>
       </c>
       <c r="K73" s="0">
-        <v>0.38659793814432958</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L73" s="0">
-        <v>0.99213137187820644</v>
+        <v>1.0776599384194312</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>0.89347248203209528</v>
+        <v>1.1396081520133887</v>
       </c>
       <c r="B74" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C74" s="0">
-        <v>0.75958356053208831</v>
+        <v>1.0905540268073388</v>
       </c>
       <c r="D74" s="0">
-        <v>0.56019041665664848</v>
+        <v>0.67078594955881943</v>
       </c>
       <c r="E74" s="0">
-        <v>0.99107968614815378</v>
+        <v>1.0799844864106916</v>
       </c>
       <c r="F74" s="0">
-        <v>0.82960375504857475</v>
+        <v>1.1206927919077239</v>
       </c>
       <c r="G74" s="0">
-        <v>0.80466706900020035</v>
+        <v>1.0661838664252656</v>
       </c>
       <c r="H74" s="0">
-        <v>0.99414872464920667</v>
+        <v>1.1532125205930797</v>
       </c>
       <c r="I74" s="0">
-        <v>0.65539909832972476</v>
+        <v>0.76661833925840528</v>
       </c>
       <c r="J74" s="0">
-        <v>1.0489510489510481</v>
+        <v>1.2513801987486188</v>
       </c>
       <c r="K74" s="0">
-        <v>0</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L74" s="0">
-        <v>0.90660280533698179</v>
+        <v>0.96880539918514519</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>0.83193856453677195</v>
+        <v>1.095303731416756</v>
       </c>
       <c r="B75" s="0">
         <v>0.087719298245613961</v>
       </c>
       <c r="C75" s="0">
-        <v>0.74943887191062464</v>
+        <v>1.0271497229231912</v>
       </c>
       <c r="D75" s="0">
-        <v>0.50248839949029833</v>
+        <v>0.62991368739932141</v>
       </c>
       <c r="E75" s="0">
-        <v>0.95050568334377439</v>
+        <v>0.9594558310212109</v>
       </c>
       <c r="F75" s="0">
-        <v>0.79139831896081148</v>
+        <v>0.96605174107630087</v>
       </c>
       <c r="G75" s="0">
-        <v>0.72420036210018035</v>
+        <v>1.0661838664252656</v>
       </c>
       <c r="H75" s="0">
-        <v>0.83508492870533357</v>
+        <v>1.4486167130602725</v>
       </c>
       <c r="I75" s="0">
-        <v>0.60177553573911091</v>
+        <v>0.7527159341423203</v>
       </c>
       <c r="J75" s="0">
-        <v>0.95693779904306131</v>
+        <v>0.86492454913507477</v>
       </c>
       <c r="K75" s="0">
         <v>0</v>
       </c>
       <c r="L75" s="0">
-        <v>0.86772618418187963</v>
+        <v>0.96414020464653283</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>0.77532736044107442</v>
+        <v>0.94269961602835406</v>
       </c>
       <c r="B76" s="0">
-        <v>0.70175438596491169</v>
+        <v>0.96491228070175361</v>
       </c>
       <c r="C76" s="0">
-        <v>0.72407715035696563</v>
+        <v>0.96374541903904343</v>
       </c>
       <c r="D76" s="0">
-        <v>0.36785035943548161</v>
+        <v>0.57702017166350061</v>
       </c>
       <c r="E76" s="0">
-        <v>0.88785464960171767</v>
+        <v>0.90098153286195815</v>
       </c>
       <c r="F76" s="0">
-        <v>0.7531928828730482</v>
+        <v>0.99152203180147647</v>
       </c>
       <c r="G76" s="0">
-        <v>0.74431703882518541</v>
+        <v>0.86501709917521541</v>
       </c>
       <c r="H76" s="0">
-        <v>0.96006362551837676</v>
+        <v>1.0339146736351748</v>
       </c>
       <c r="I76" s="0">
-        <v>0.55609620464340281</v>
+        <v>0.71696689241524436</v>
       </c>
       <c r="J76" s="0">
-        <v>0.93853514906146396</v>
+        <v>0.86492454913507477</v>
       </c>
       <c r="K76" s="0">
         <v>0</v>
       </c>
       <c r="L76" s="0">
-        <v>0.80396852548751208</v>
+        <v>0.93614903741485944</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>0.75809786354238395</v>
+        <v>0.92793147582947644</v>
       </c>
       <c r="B77" s="0">
-        <v>0.70175438596491169</v>
+        <v>0.96491228070175361</v>
       </c>
       <c r="C77" s="0">
-        <v>0.71393246173550196</v>
+        <v>0.92443475063087188</v>
       </c>
       <c r="D77" s="0">
-        <v>0.30053133940807319</v>
+        <v>0.49527564734450463</v>
       </c>
       <c r="E77" s="0">
-        <v>0.78104955398430664</v>
+        <v>0.80789999701661674</v>
       </c>
       <c r="F77" s="0">
-        <v>0.75137357639267843</v>
+        <v>0.96969035403704029</v>
       </c>
       <c r="G77" s="0">
-        <v>0.82478374572520541</v>
+        <v>0.76443371555019046</v>
       </c>
       <c r="H77" s="0">
-        <v>0.73282963131284373</v>
+        <v>1.0055104243594832</v>
       </c>
       <c r="I77" s="0">
-        <v>0.46473754245198662</v>
+        <v>0.62759428809755458</v>
       </c>
       <c r="J77" s="0">
-        <v>1.0305483989694506</v>
+        <v>0.86492454913507477</v>
       </c>
       <c r="K77" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L77" s="0">
-        <v>0.78219761764065487</v>
+        <v>0.88327683264392043</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>0.67195037904893118</v>
+        <v>0.84424534803583662</v>
       </c>
       <c r="B78" s="0">
         <v>0.78947368421052566</v>
       </c>
       <c r="C78" s="0">
-        <v>0.61755791983159758</v>
+        <v>0.81791552010550406</v>
       </c>
       <c r="D78" s="0">
-        <v>0.27168033082489818</v>
+        <v>0.45921188661553586</v>
       </c>
       <c r="E78" s="0">
-        <v>0.70109490139920583</v>
+        <v>0.72138190280139558</v>
       </c>
       <c r="F78" s="0">
-        <v>0.64221518757049756</v>
+        <v>0.90601462722410131</v>
       </c>
       <c r="G78" s="0">
-        <v>0.50291691812512529</v>
+        <v>0.78455039227519552</v>
       </c>
       <c r="H78" s="0">
-        <v>0.56240413565869407</v>
+        <v>0.98278702493893</v>
       </c>
       <c r="I78" s="0">
-        <v>0.49850052630533609</v>
+        <v>0.5382216837798649</v>
       </c>
       <c r="J78" s="0">
-        <v>0.80971659919028272</v>
+        <v>1.324990798675008</v>
       </c>
       <c r="K78" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L78" s="0">
-        <v>0.77442229340963453</v>
+        <v>0.78841787702547128</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>0.60549374815398194</v>
+        <v>0.85409077483508822</v>
       </c>
       <c r="B79" s="0">
-        <v>1.4035087719298234</v>
+        <v>1.0526315789473675</v>
       </c>
       <c r="C79" s="0">
-        <v>0.53766849693757157</v>
+        <v>0.79635805678489391</v>
       </c>
       <c r="D79" s="0">
-        <v>0.26927608010963361</v>
+        <v>0.37265886086601074</v>
       </c>
       <c r="E79" s="0">
-        <v>0.61278677764849732</v>
+        <v>0.7154151376831045</v>
       </c>
       <c r="F79" s="0">
-        <v>0.67314339773678211</v>
+        <v>0.80777207728413858</v>
       </c>
       <c r="G79" s="0">
-        <v>0.78455039227519552</v>
+        <v>0.76443371555019046</v>
       </c>
       <c r="H79" s="0">
-        <v>0.68738283247173715</v>
+        <v>0.85780832812588681</v>
       </c>
       <c r="I79" s="0">
-        <v>0.46473754245198662</v>
+        <v>0.55212408889594988</v>
       </c>
       <c r="J79" s="0">
-        <v>0.5152741994847253</v>
+        <v>1.10415899889584</v>
       </c>
       <c r="K79" s="0">
         <v>0</v>
       </c>
       <c r="L79" s="0">
-        <v>0.67334307840636898</v>
+        <v>0.77286722856343038</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>0.55134390075809736</v>
+        <v>0.74332972334350622</v>
       </c>
       <c r="B80" s="0">
-        <v>1.3157894736842093</v>
+        <v>1.0526315789473675</v>
       </c>
       <c r="C80" s="0">
-        <v>0.53513232478220574</v>
+        <v>0.66574519078354977</v>
       </c>
       <c r="D80" s="0">
-        <v>0.26927608010963361</v>
+        <v>0.31014834226913152</v>
       </c>
       <c r="E80" s="0">
-        <v>0.5525224499537571</v>
+        <v>0.63725051463349092</v>
       </c>
       <c r="F80" s="0">
-        <v>0.62584142924717034</v>
+        <v>0.77866317359822368</v>
       </c>
       <c r="G80" s="0">
-        <v>0.54315027157513529</v>
+        <v>0.76443371555019046</v>
       </c>
       <c r="H80" s="0">
-        <v>0.65897858319604552</v>
+        <v>0.92597852638754685</v>
       </c>
       <c r="I80" s="0">
-        <v>0.42700244285118427</v>
+        <v>0.49254235268415675</v>
       </c>
       <c r="J80" s="0">
-        <v>0.71770334928229607</v>
+        <v>0.84652189915347742</v>
       </c>
       <c r="K80" s="0">
         <v>0</v>
       </c>
       <c r="L80" s="0">
-        <v>0.63757658694367503</v>
+        <v>0.65157217055951178</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>0.51688490696071632</v>
+        <v>0.72610022644481576</v>
       </c>
       <c r="B81" s="0">
-        <v>1.4912280701754372</v>
+        <v>1.1403508771929816</v>
       </c>
       <c r="C81" s="0">
-        <v>0.41593223348000824</v>
+        <v>0.69237499841489181</v>
       </c>
       <c r="D81" s="0">
-        <v>0.25965907724857523</v>
+        <v>0.3005313394080732</v>
       </c>
       <c r="E81" s="0">
-        <v>0.48688803365255484</v>
+        <v>0.51373847668486483</v>
       </c>
       <c r="F81" s="0">
-        <v>0.64039588109012779</v>
+        <v>0.70225230142269701</v>
       </c>
       <c r="G81" s="0">
-        <v>0.5833836250251454</v>
+        <v>0.68396700865017046</v>
       </c>
       <c r="H81" s="0">
-        <v>0.63057433392035389</v>
+        <v>0.73851048116798212</v>
       </c>
       <c r="I81" s="0">
-        <v>0.36543464876566473</v>
+        <v>0.48062600544179812</v>
       </c>
       <c r="J81" s="0">
-        <v>0.62569009937430942</v>
+        <v>0.93853514906146396</v>
       </c>
       <c r="K81" s="0">
         <v>0</v>
       </c>
       <c r="L81" s="0">
-        <v>0.60958541971200153</v>
+        <v>0.66556775417534852</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>0.50211676676184425</v>
+        <v>0.66948902234912566</v>
       </c>
       <c r="B82" s="0">
-        <v>0.87719298245614929</v>
+        <v>1.315789473684224</v>
       </c>
       <c r="C82" s="0">
-        <v>0.34111515489671784</v>
+        <v>0.61755791983160446</v>
       </c>
       <c r="D82" s="0">
-        <v>0.21638256437381512</v>
+        <v>0.23561657009593201</v>
       </c>
       <c r="E82" s="0">
-        <v>0.43855723619440168</v>
+        <v>0.48987141621170582</v>
       </c>
       <c r="F82" s="0">
-        <v>0.48211621729797099</v>
+        <v>0.60764836444348036</v>
       </c>
       <c r="G82" s="0">
-        <v>0.80466706900020935</v>
+        <v>0.72420036210018846</v>
       </c>
       <c r="H82" s="0">
-        <v>0.61353178435494571</v>
+        <v>0.59648923478953064</v>
       </c>
       <c r="I82" s="0">
-        <v>0.32571349129113952</v>
+        <v>0.39522551687156565</v>
       </c>
       <c r="J82" s="0">
-        <v>0.55207949944792611</v>
+        <v>0.73610599926390152</v>
       </c>
       <c r="K82" s="0">
         <v>0</v>
       </c>
       <c r="L82" s="0">
-        <v>0.5738189282493138</v>
+        <v>0.62980126271266146</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>0.44550556266614116</v>
+        <v>0.60057103475435603</v>
       </c>
       <c r="B83" s="0">
         <v>0.96491228070175361</v>
       </c>
       <c r="C83" s="0">
-        <v>0.35125984351817768</v>
+        <v>0.56556639064659664</v>
       </c>
       <c r="D83" s="0">
-        <v>0.23080806866540021</v>
+        <v>0.28370158440122112</v>
       </c>
       <c r="E83" s="0">
-        <v>0.38425967361794772</v>
+        <v>0.40812673409111217</v>
       </c>
       <c r="F83" s="0">
-        <v>0.51850234690535923</v>
+        <v>0.60582905796310393</v>
       </c>
       <c r="G83" s="0">
-        <v>0.44256688795011023</v>
+        <v>0.54315027157513529</v>
       </c>
       <c r="H83" s="0">
-        <v>0.54536158609327912</v>
+        <v>0.64193603363063056</v>
       </c>
       <c r="I83" s="0">
-        <v>0.28202021806915428</v>
+        <v>0.39323945899783486</v>
       </c>
       <c r="J83" s="0">
-        <v>0.36805299963194671</v>
+        <v>0.84652189915347742</v>
       </c>
       <c r="K83" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L83" s="0">
-        <v>0.53960750163281768</v>
+        <v>0.61580567909681783</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>0.39135571527025664</v>
+        <v>0.56365068425716203</v>
       </c>
       <c r="B84" s="0">
-        <v>0.61403508771929771</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C84" s="0">
-        <v>0.27517467885720059</v>
+        <v>0.50850251715086381</v>
       </c>
       <c r="D84" s="0">
-        <v>0.22599956723487105</v>
+        <v>0.28610583511648569</v>
       </c>
       <c r="E84" s="0">
-        <v>0.30251499149735944</v>
+        <v>0.34607237686088455</v>
       </c>
       <c r="F84" s="0">
-        <v>0.44209147472983257</v>
+        <v>0.59127460612014648</v>
       </c>
       <c r="G84" s="0">
-        <v>0.38221685777509523</v>
+        <v>0.44256688795011023</v>
       </c>
       <c r="H84" s="0">
-        <v>0.4715105379764809</v>
+        <v>0.64193603363063056</v>
       </c>
       <c r="I84" s="0">
-        <v>0.28400627594288075</v>
+        <v>0.38330916962920264</v>
       </c>
       <c r="J84" s="0">
-        <v>0.58888479941111471</v>
+        <v>0.92013249907986661</v>
       </c>
       <c r="K84" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L84" s="0">
-        <v>0.39654153578204171</v>
+        <v>0.55049295555624622</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>0.38151028847100488</v>
+        <v>0.51442355026090336</v>
       </c>
       <c r="B85" s="0">
-        <v>0.61403508771929771</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C85" s="0">
-        <v>0.22445123574988252</v>
+        <v>0.4286130942568378</v>
       </c>
       <c r="D85" s="0">
-        <v>0.22599956723487105</v>
+        <v>0.25965907724857523</v>
       </c>
       <c r="E85" s="0">
-        <v>0.33115546406515678</v>
+        <v>0.34547570034905545</v>
       </c>
       <c r="F85" s="0">
-        <v>0.38751228031874213</v>
+        <v>0.54761125059127413</v>
       </c>
       <c r="G85" s="0">
-        <v>0.16093341380004009</v>
+        <v>0.38221685777509523</v>
       </c>
       <c r="H85" s="0">
-        <v>0.41470203942509765</v>
+        <v>0.56240413565869407</v>
       </c>
       <c r="I85" s="0">
-        <v>0.26017358145816344</v>
+        <v>0.37536493813429689</v>
       </c>
       <c r="J85" s="0">
-        <v>0.4600662495399333</v>
+        <v>0.5152741994847253</v>
       </c>
       <c r="K85" s="0">
         <v>0</v>
       </c>
       <c r="L85" s="0">
-        <v>0.47584984293845012</v>
+        <v>0.52716698286318486</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>0.31505365757605563</v>
+        <v>0.48488726986314812</v>
       </c>
       <c r="B86" s="0">
-        <v>0.35087719298245584</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C86" s="0">
-        <v>0.20923420281768709</v>
+        <v>0.39944711447012987</v>
       </c>
       <c r="D86" s="0">
-        <v>0.15627629649219807</v>
+        <v>0.19474430793643144</v>
       </c>
       <c r="E86" s="0">
-        <v>0.28759807870163168</v>
+        <v>0.28998478474894812</v>
       </c>
       <c r="F86" s="0">
-        <v>0.35294545719171821</v>
+        <v>0.46756176545500811</v>
       </c>
       <c r="G86" s="0">
-        <v>0.34198350432508523</v>
+        <v>0.54315027157513529</v>
       </c>
       <c r="H86" s="0">
-        <v>0.32948929159802276</v>
+        <v>0.53399988638300244</v>
       </c>
       <c r="I86" s="0">
-        <v>0.24825723421580481</v>
+        <v>0.27010387082679566</v>
       </c>
       <c r="J86" s="0">
         <v>0.4600662495399333</v>
       </c>
       <c r="K86" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L86" s="0">
-        <v>0.36855036855036821</v>
+        <v>0.45718906478400107</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>0.27074923697942282</v>
+        <v>0.42089199566801189</v>
       </c>
       <c r="B87" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C87" s="0">
-        <v>0.12934477992366109</v>
+        <v>0.34745558528512888</v>
       </c>
       <c r="D87" s="0">
-        <v>0.12742528790902305</v>
+        <v>0.2356165700959294</v>
       </c>
       <c r="E87" s="0">
-        <v>0.25179748799188495</v>
+        <v>0.26850443032310012</v>
       </c>
       <c r="F87" s="0">
-        <v>0.34202961830950013</v>
+        <v>0.46756176545500811</v>
       </c>
       <c r="G87" s="0">
-        <v>0.24140012070006014</v>
+        <v>0.32186682760008018</v>
       </c>
       <c r="H87" s="0">
-        <v>0.22723399420553292</v>
+        <v>0.61353178435493894</v>
       </c>
       <c r="I87" s="0">
-        <v>0.18867549800401168</v>
+        <v>0.27606204444797494</v>
       </c>
       <c r="J87" s="0">
-        <v>0.25763709974236265</v>
+        <v>0.49687154950312801</v>
       </c>
       <c r="K87" s="0">
         <v>0</v>
       </c>
       <c r="L87" s="0">
-        <v>0.34677946070351101</v>
+        <v>0.37632569278138867</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>0.25844245348035816</v>
+        <v>0.40120114206950841</v>
       </c>
       <c r="B88" s="0">
         <v>0.087719298245613961</v>
       </c>
       <c r="C88" s="0">
-        <v>0.1268086077682952</v>
+        <v>0.27771085101256649</v>
       </c>
       <c r="D88" s="0">
-        <v>0.093765777895318841</v>
+        <v>0.15146779506166888</v>
       </c>
       <c r="E88" s="0">
-        <v>0.22494704495957496</v>
+        <v>0.22196366240042942</v>
       </c>
       <c r="F88" s="0">
-        <v>0.24742568133027668</v>
+        <v>0.38387366735800277</v>
       </c>
       <c r="G88" s="0">
         <v>0.22128344397505512</v>
       </c>
       <c r="H88" s="0">
-        <v>0.24427654377094793</v>
+        <v>0.60785093449980066</v>
       </c>
       <c r="I88" s="0">
-        <v>0.13505193541339783</v>
+        <v>0.26215963933188991</v>
       </c>
       <c r="J88" s="0">
-        <v>0.38645564961354401</v>
+        <v>0.57048214942951736</v>
       </c>
       <c r="K88" s="0">
         <v>0</v>
       </c>
       <c r="L88" s="0">
-        <v>0.30790283954840891</v>
+        <v>0.40898205455167447</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>0.2338288864822288</v>
+        <v>0.35443536477306259</v>
       </c>
       <c r="B89" s="0">
         <v>0</v>
       </c>
       <c r="C89" s="0">
-        <v>0.077353250738660076</v>
+        <v>0.24220444083744383</v>
       </c>
       <c r="D89" s="0">
-        <v>0.084148775034260492</v>
+        <v>0.16108479792272723</v>
       </c>
       <c r="E89" s="0">
-        <v>0.15692592261105628</v>
+        <v>0.21122348518750539</v>
       </c>
       <c r="F89" s="0">
-        <v>0.22377469708547082</v>
+        <v>0.4220791034457661</v>
       </c>
       <c r="G89" s="0">
-        <v>0.26151679742506517</v>
+        <v>0.24140012070006015</v>
       </c>
       <c r="H89" s="0">
-        <v>0.22723399420553292</v>
+        <v>0.45446798841106584</v>
       </c>
       <c r="I89" s="0">
-        <v>0.13306587753967139</v>
+        <v>0.18271732438283236</v>
       </c>
       <c r="J89" s="0">
-        <v>0.25763709974236265</v>
+        <v>0.40485829959514136</v>
       </c>
       <c r="K89" s="0">
         <v>0</v>
       </c>
       <c r="L89" s="0">
-        <v>0.26902621839330676</v>
+        <v>0.32656361770285791</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>0.22398345968297706</v>
+        <v>0.27321059367923578</v>
       </c>
       <c r="B90" s="0">
         <v>0</v>
       </c>
       <c r="C90" s="0">
-        <v>0.059600045651098742</v>
+        <v>0.20035760027390642</v>
       </c>
       <c r="D90" s="0">
-        <v>0.12502103719375846</v>
+        <v>0.084148775034260492</v>
       </c>
       <c r="E90" s="0">
-        <v>0.14558906888630316</v>
+        <v>0.17184283540678405</v>
       </c>
       <c r="F90" s="0">
-        <v>0.1673761961940107</v>
+        <v>0.32747516646654268</v>
       </c>
       <c r="G90" s="0">
-        <v>0.48280024140012029</v>
+        <v>0.26151679742506517</v>
       </c>
       <c r="H90" s="0">
-        <v>0.19882974492984132</v>
+        <v>0.30676589217746947</v>
       </c>
       <c r="I90" s="0">
-        <v>0.12512164604476564</v>
+        <v>0.15292645627693577</v>
       </c>
       <c r="J90" s="0">
-        <v>0.27603974972396</v>
+        <v>0.57048214942951736</v>
       </c>
       <c r="K90" s="0">
         <v>0</v>
       </c>
       <c r="L90" s="0">
-        <v>0.23325972693061278</v>
+        <v>0.29235219108636806</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>0.16491089888746663</v>
+        <v>0.29536280397755216</v>
       </c>
       <c r="B91" s="0">
         <v>0.087719298245613961</v>
       </c>
       <c r="C91" s="0">
-        <v>0.048187270951952174</v>
+        <v>0.14329372677817359</v>
       </c>
       <c r="D91" s="0">
-        <v>0.06010626788161464</v>
+        <v>0.052893515735820879</v>
       </c>
       <c r="E91" s="0">
-        <v>0.11933530236582227</v>
+        <v>0.13544556818520828</v>
       </c>
       <c r="F91" s="0">
-        <v>0.15100243787068357</v>
+        <v>0.35476476367208787</v>
       </c>
       <c r="G91" s="0">
-        <v>0.28163347415007012</v>
+        <v>0.30175015087507517</v>
       </c>
       <c r="H91" s="0">
-        <v>0.18746804521956467</v>
+        <v>0.28972334261205451</v>
       </c>
       <c r="I91" s="0">
-        <v>0.11519135667613344</v>
+        <v>0.1807312665091059</v>
       </c>
       <c r="J91" s="0">
-        <v>0.18402649981597335</v>
+        <v>0.40485829959514136</v>
       </c>
       <c r="K91" s="0">
         <v>0</v>
       </c>
       <c r="L91" s="0">
-        <v>0.20060336516032701</v>
+        <v>0.27835660747053126</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>0.12306783499064673</v>
+        <v>0.24121295658166758</v>
       </c>
       <c r="B92" s="0">
         <v>0</v>
       </c>
       <c r="C92" s="0">
-        <v>0.031702151942073799</v>
+        <v>0.13948946854512473</v>
       </c>
       <c r="D92" s="0">
-        <v>0.052893515735820879</v>
+        <v>0.091361527180054247</v>
       </c>
       <c r="E92" s="0">
-        <v>0.093081535845341373</v>
+        <v>0.10799844864106915</v>
       </c>
       <c r="F92" s="0">
-        <v>0.10370046938107184</v>
+        <v>0.27471527853582189</v>
       </c>
       <c r="G92" s="0">
-        <v>0.14081673707503506</v>
+        <v>0.10058338362502504</v>
       </c>
       <c r="H92" s="0">
-        <v>0.17610634550928805</v>
+        <v>0.29540419246719279</v>
       </c>
       <c r="I92" s="0">
-        <v>0.065539909832972476</v>
+        <v>0.12909376179221851</v>
       </c>
       <c r="J92" s="0">
-        <v>0.14722119985277868</v>
+        <v>0.34965034965034936</v>
       </c>
       <c r="K92" s="0">
-        <v>0.38659793814432958</v>
+        <v>0</v>
       </c>
       <c r="L92" s="0">
-        <v>0.1570615494666126</v>
+        <v>0.24725531054644959</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>0.08122477109382685</v>
+        <v>0.2535197400807323</v>
       </c>
       <c r="B93" s="0">
-        <v>0</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C93" s="0">
-        <v>0.025361721553659039</v>
+        <v>0.093838369748538444</v>
       </c>
       <c r="D93" s="0">
-        <v>0.074531772173202157</v>
+        <v>0.079340273603731332</v>
       </c>
       <c r="E93" s="0">
-        <v>0.079357976073271802</v>
+        <v>0.081744682120588247</v>
       </c>
       <c r="F93" s="0">
-        <v>0.065495033293308524</v>
+        <v>0.19284648691918624</v>
       </c>
       <c r="G93" s="0">
-        <v>0.12070006035003007</v>
+        <v>0.14081673707503506</v>
       </c>
       <c r="H93" s="0">
-        <v>0.13634039652331978</v>
+        <v>0.20451059478497965</v>
       </c>
       <c r="I93" s="0">
-        <v>0.041707215348255215</v>
+        <v>0.11916347242358631</v>
       </c>
       <c r="J93" s="0">
-        <v>0.165623849834376</v>
+        <v>0.31284504968715471</v>
       </c>
       <c r="K93" s="0">
-        <v>0.25773195876288635</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L93" s="0">
-        <v>0.11040960408049005</v>
+        <v>0.18660778154449026</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>0.088608841193266633</v>
+        <v>0.22890617308260547</v>
       </c>
       <c r="B94" s="0">
-        <v>0</v>
+        <v>0.17543859649122986</v>
       </c>
       <c r="C94" s="0">
-        <v>0.011412774699146694</v>
+        <v>0.078621336816343895</v>
       </c>
       <c r="D94" s="0">
-        <v>0.062510518596879922</v>
+        <v>0.084148775034261422</v>
       </c>
       <c r="E94" s="0">
-        <v>0.053700886064620611</v>
+        <v>0.060861004206570035</v>
       </c>
       <c r="F94" s="0">
-        <v>0.058217807371830452</v>
+        <v>0.18920787395844899</v>
       </c>
       <c r="G94" s="0">
-        <v>0.040233353450010473</v>
+        <v>0.1207000603500314</v>
       </c>
       <c r="H94" s="0">
-        <v>0.10225529739249097</v>
+        <v>0.2101914446401203</v>
       </c>
       <c r="I94" s="0">
-        <v>0.047665388969435056</v>
+        <v>0.10724712518122888</v>
       </c>
       <c r="J94" s="0">
-        <v>0.14722119985278029</v>
+        <v>0.33124769966875567</v>
       </c>
       <c r="K94" s="0">
-        <v>0.38659793814433385</v>
+        <v>0</v>
       </c>
       <c r="L94" s="0">
-        <v>0.082418436848817431</v>
+        <v>0.14773116038938974</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>0.078763414394013909</v>
+        <v>0.15506547208821489</v>
       </c>
       <c r="B95" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C95" s="0">
-        <v>0.022825549398293135</v>
+        <v>0.05199152918500103</v>
       </c>
       <c r="D95" s="0">
-        <v>0.028851008583175027</v>
+        <v>0.084148775034260492</v>
       </c>
       <c r="E95" s="0">
-        <v>0.045347414899012464</v>
+        <v>0.062054357230227578</v>
       </c>
       <c r="F95" s="0">
-        <v>0.038205436087763313</v>
+        <v>0.10188116290070216</v>
       </c>
       <c r="G95" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.040233353450010022</v>
       </c>
       <c r="H95" s="0">
-        <v>0.045446798841106584</v>
+        <v>0.18746804521956467</v>
       </c>
       <c r="I95" s="0">
-        <v>0.021846636610990827</v>
+        <v>0.07149808345415179</v>
       </c>
       <c r="J95" s="0">
-        <v>0.18402649981597335</v>
+        <v>0.23923444976076533</v>
       </c>
       <c r="K95" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L95" s="0">
-        <v>0.091748825926041028</v>
+        <v>0.1041893446956737</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>0.073840700994388039</v>
+        <v>0.11322240819139499</v>
       </c>
       <c r="B96" s="0">
         <v>0.17543859649122792</v>
       </c>
       <c r="C96" s="0">
-        <v>0.011412774699146568</v>
+        <v>0.039310668408171511</v>
       </c>
       <c r="D96" s="0">
-        <v>0.036063760728968788</v>
+        <v>0.088957276464789667</v>
       </c>
       <c r="E96" s="0">
-        <v>0.025060413496822677</v>
+        <v>0.038783973268892234</v>
       </c>
       <c r="F96" s="0">
-        <v>0.0291089036859149</v>
+        <v>0.1164356147436596</v>
       </c>
       <c r="G96" s="0">
-        <v>0.080466706900020044</v>
+        <v>0.14081673707503506</v>
       </c>
       <c r="H96" s="0">
-        <v>0.090893597682213167</v>
+        <v>0.22723399420553292</v>
       </c>
       <c r="I96" s="0">
-        <v>0.029790868105896578</v>
+        <v>0.061567794085519593</v>
       </c>
       <c r="J96" s="0">
-        <v>0.055207949944792008</v>
+        <v>0.23923444976076533</v>
       </c>
       <c r="K96" s="0">
-        <v>1.417525773195875</v>
+        <v>0</v>
       </c>
       <c r="L96" s="0">
-        <v>0.059092464155755239</v>
+        <v>0.099524150157061467</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>0.029536280397755216</v>
+        <v>0.10829969479176912</v>
       </c>
       <c r="B97" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C97" s="0">
-        <v>0.0050723443107318078</v>
+        <v>0.024093635475976087</v>
       </c>
       <c r="D97" s="0">
-        <v>0.012021253576322928</v>
+        <v>0.045680763590027124</v>
       </c>
       <c r="E97" s="0">
-        <v>0.021480354425848006</v>
+        <v>0.028640472567797344</v>
       </c>
       <c r="F97" s="0">
-        <v>0.0090965324018484079</v>
+        <v>0.092784630498853757</v>
       </c>
       <c r="G97" s="0">
-        <v>0.10058338362502504</v>
+        <v>0.12070006035003007</v>
       </c>
       <c r="H97" s="0">
-        <v>0.039765948985968268</v>
+        <v>0.096574447537351504</v>
       </c>
       <c r="I97" s="0">
-        <v>0.017874520863537947</v>
+        <v>0.021846636610990827</v>
       </c>
       <c r="J97" s="0">
-        <v>0.092013249907986677</v>
+        <v>0.12881854987118133</v>
       </c>
       <c r="K97" s="0">
-        <v>1.0309278350515454</v>
+        <v>0</v>
       </c>
       <c r="L97" s="0">
-        <v>0.041986750847510308</v>
+        <v>0.083973501695020617</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>0.029536280397755216</v>
+        <v>0.08122477109382685</v>
       </c>
       <c r="B98" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C98" s="0">
-        <v>0.001268086077682952</v>
+        <v>0.016485119009878375</v>
       </c>
       <c r="D98" s="0">
-        <v>0.0072127521457937566</v>
+        <v>0.033659510013704201</v>
       </c>
       <c r="E98" s="0">
-        <v>0.017900295354873339</v>
+        <v>0.021480354425848006</v>
       </c>
       <c r="F98" s="0">
-        <v>0.021831677764436178</v>
+        <v>0.061856420332569169</v>
       </c>
       <c r="G98" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.12070006035003007</v>
       </c>
       <c r="H98" s="0">
-        <v>0.039765948985968268</v>
+        <v>0.090893597682213168</v>
       </c>
       <c r="I98" s="0">
-        <v>0.0079442314949057548</v>
+        <v>0.035749041727075895</v>
       </c>
       <c r="J98" s="0">
-        <v>0.055207949944792008</v>
+        <v>0.165623849834376</v>
       </c>
       <c r="K98" s="0">
-        <v>1.9329896907216479</v>
+        <v>0.38659793814432958</v>
       </c>
       <c r="L98" s="0">
-        <v>0.012440518769632683</v>
+        <v>0.046651945386122565</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>0.024613566998129346</v>
+        <v>0.051688490696071628</v>
       </c>
       <c r="B99" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C99" s="0">
-        <v>0</v>
+        <v>0.01268086077682952</v>
       </c>
       <c r="D99" s="0">
-        <v>0.004808501430529172</v>
+        <v>0.026446757867910439</v>
       </c>
       <c r="E99" s="0">
-        <v>0.011336853724753116</v>
+        <v>0.0077567946537784472</v>
       </c>
       <c r="F99" s="0">
-        <v>0.0090965324018484079</v>
+        <v>0.032747516646654262</v>
       </c>
       <c r="G99" s="0">
-        <v>0</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H99" s="0">
-        <v>0.005680849855138323</v>
+        <v>0.079531897971936536</v>
       </c>
       <c r="I99" s="0">
-        <v>0.0059581736211793161</v>
+        <v>0.019860578737264385</v>
       </c>
       <c r="J99" s="0">
-        <v>0.03680529996319467</v>
+        <v>0.165623849834376</v>
       </c>
       <c r="K99" s="0">
-        <v>0.77319587628865916</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L99" s="0">
-        <v>0.010885453923428597</v>
+        <v>0.037321556308898045</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>0.034458993797381085</v>
+        <v>0.14029733188933727</v>
       </c>
       <c r="B100" s="0">
-        <v>1.0526315789473675</v>
+        <v>0.87719298245613953</v>
       </c>
       <c r="C100" s="0">
-        <v>0.001268086077682952</v>
+        <v>0.021557463320610183</v>
       </c>
       <c r="D100" s="0">
-        <v>0.0072127521457937566</v>
+        <v>0.040872262159497956</v>
       </c>
       <c r="E100" s="0">
-        <v>0.010740177212924003</v>
+        <v>0.015513589307556894</v>
       </c>
       <c r="F100" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0.063675726812938857</v>
       </c>
       <c r="G100" s="0">
         <v>0.10058338362502504</v>
       </c>
       <c r="H100" s="0">
-        <v>0.039765948985968268</v>
+        <v>0.23859569391580959</v>
       </c>
       <c r="I100" s="0">
-        <v>0.011916347242358632</v>
+        <v>0.02780481023217014</v>
       </c>
       <c r="J100" s="0">
-        <v>0.073610599926389339</v>
+        <v>0.5152741994847253</v>
       </c>
       <c r="K100" s="0">
-        <v>3.479381443298966</v>
+        <v>9.2783505154639094</v>
       </c>
       <c r="L100" s="0">
-        <v>0.02021584300065311</v>
+        <v>0.054427269617142983</v>
       </c>
     </row>
   </sheetData>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0005_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0005_ses-01_WMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
